--- a/DOC/assets/365CMS_Asset_Uebersicht.xlsx
+++ b/DOC/assets/365CMS_Asset_Uebersicht.xlsx
@@ -769,11 +769,10 @@
     <row r="2">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>Geprüft gegen composer.json / installed.json / JS-Lizenzheader sowie Packagist- und npm-Registry. „Upstream aktuell“ = neuester Stable-Stand am 2026-10-04.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Geprüft gegen composer.json / installed.json / JS-Lizenzheader sowie Packagist- und npm-Registry. „Upstream aktuell“ = neuester Stable-Stand am 2026-10-04. Runtime-Stände nach dem Asset-Update vom 2026-10-04 (365CMS 3.4.18).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
@@ -834,7 +833,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.41.1</t>
+          <t>3.48.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1002,7 +1001,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0.5</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1044,7 +1043,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.31.6</t>
+          <t>2.31.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2220,7 +2219,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Snapshot</t>
+          <t>7.2.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2262,7 +2261,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.0.3</t>
+          <t>4.0.8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2472,7 +2471,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2514,7 +2513,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2598,7 +2597,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.0.2</t>
+          <t>3.0.3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2640,7 +2639,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5.0.3</t>
+          <t>5.3.0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2808,7 +2807,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2850,7 +2849,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2892,7 +2891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.6.0</t>
+          <t>0.14.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2934,7 +2933,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2976,7 +2975,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3018,7 +3017,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3060,7 +3059,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3102,7 +3101,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3144,7 +3143,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3186,7 +3185,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3522,7 +3521,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3.11.4</t>
+          <t>3.14.2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3564,7 +3563,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8.0.8</t>
+          <t>8.1.0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3648,7 +3647,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.3x/1.4x</t>
+          <t>1.43.0</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3690,7 +3689,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.3x/1.4x</t>
+          <t>1.43.0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3732,7 +3731,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.3x/1.4x</t>
+          <t>1.43.0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3774,7 +3773,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.3x/1.4x</t>
+          <t>1.43.0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3816,7 +3815,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.3x/1.4x</t>
+          <t>1.43.0</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3858,7 +3857,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.3x/1.4x</t>
+          <t>1.43.0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4110,7 +4109,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3.1.5</t>
+          <t>3.1.6</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4236,7 +4235,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.10.0</t>
+          <t>2.11.0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4278,7 +4277,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>8.9.0</t>
+          <t>9.5.0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
